--- a/data/trans_orig/IP31A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31A-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14428</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28083</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35421</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39504</t>
+          <t>39696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59304</t>
+          <t>59912</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48957</t>
+          <t>48732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66124</t>
+          <t>66465</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60013</t>
+          <t>59564</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>78694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114007</t>
+          <t>114392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140038</t>
+          <t>139396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27831</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43750</t>
+          <t>43295</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20662</t>
+          <t>20504</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35231</t>
+          <t>35869</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51693</t>
+          <t>52592</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>74135</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17487</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28756</t>
+          <t>28890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57002</t>
+          <t>56937</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57784</t>
+          <t>57856</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>82198</t>
+          <t>82243</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73398</t>
+          <t>73677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92042</t>
+          <t>92448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78681</t>
+          <t>78165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99885</t>
+          <t>99006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157230</t>
+          <t>156541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185851</t>
+          <t>185881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39141</t>
+          <t>39150</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56612</t>
+          <t>56765</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>32884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50047</t>
+          <t>50275</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77316</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102076</t>
+          <t>102384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>26767</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26989</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>42760</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45179</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64583</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57182</t>
+          <t>56846</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73349</t>
+          <t>73205</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60328</t>
+          <t>60027</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>77951</t>
+          <t>78054</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>123523</t>
+          <t>121795</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>146977</t>
+          <t>147152</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>33800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26052</t>
+          <t>25836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34560</t>
+          <t>35142</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53379</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20574</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45290</t>
+          <t>45831</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53073</t>
+          <t>52176</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77889</t>
+          <t>76205</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80077</t>
+          <t>79822</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102464</t>
+          <t>102736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70929</t>
+          <t>72203</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91998</t>
+          <t>93469</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158550</t>
+          <t>159437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>191022</t>
+          <t>190853</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>44770</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>65451</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42002</t>
+          <t>42203</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>61292</t>
+          <t>61890</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91793</t>
+          <t>90271</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>120485</t>
+          <t>119507</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>11987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77144</t>
+          <t>76393</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>104259</t>
+          <t>105420</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>129962</t>
+          <t>128794</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>163040</t>
+          <t>162635</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>214695</t>
+          <t>216187</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>258192</t>
+          <t>258054</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>277624</t>
+          <t>277982</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>317411</t>
+          <t>316381</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>290545</t>
+          <t>289380</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>330352</t>
+          <t>330766</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>580239</t>
+          <t>581618</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>636357</t>
+          <t>636317</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145592</t>
+          <t>145990</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>179385</t>
+          <t>180674</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121191</t>
+          <t>121687</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154309</t>
+          <t>156329</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>275191</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>323239</t>
+          <t>324054</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14378</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>32258</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>51239</t>
+          <t>52842</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>27915</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>31221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33548</t>
+          <t>33531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53584</t>
+          <t>54482</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42292</t>
+          <t>43471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60087</t>
+          <t>60710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70416</t>
+          <t>69975</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>89365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117838</t>
+          <t>118417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145250</t>
+          <t>146125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36532</t>
+          <t>36264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54433</t>
+          <t>53311</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60966</t>
+          <t>60756</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83891</t>
+          <t>84436</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26470</t>
+          <t>26069</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44628</t>
+          <t>44548</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48264</t>
+          <t>48242</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72775</t>
+          <t>70867</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78353</t>
+          <t>76200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98413</t>
+          <t>97373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87859</t>
+          <t>88383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109086</t>
+          <t>110184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171304</t>
+          <t>172021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201000</t>
+          <t>201460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31920</t>
+          <t>31922</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49676</t>
+          <t>49424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31369</t>
+          <t>31736</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>49561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69100</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94654</t>
+          <t>94452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>31020</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>25268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>17580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>31427</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33019</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52953</t>
+          <t>52291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62721</t>
+          <t>63239</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80967</t>
+          <t>80655</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66470</t>
+          <t>66654</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84864</t>
+          <t>85511</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>135092</t>
+          <t>133787</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160681</t>
+          <t>159958</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39777</t>
+          <t>40284</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28501</t>
+          <t>29225</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44497</t>
+          <t>45209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56939</t>
+          <t>57674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79538</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20591</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33626</t>
+          <t>33723</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>40877</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62158</t>
+          <t>61812</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63718</t>
+          <t>63213</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91116</t>
+          <t>88790</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73270</t>
+          <t>71432</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94733</t>
+          <t>94355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71234</t>
+          <t>71937</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>93130</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>149749</t>
+          <t>149406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>182765</t>
+          <t>181429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>38598</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57908</t>
+          <t>58228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28908</t>
+          <t>28365</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46395</t>
+          <t>46802</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73202</t>
+          <t>72996</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>99646</t>
+          <t>99716</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>13468</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>28529</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74064</t>
+          <t>73427</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102636</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114402</t>
+          <t>115127</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>149786</t>
+          <t>150184</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>200103</t>
+          <t>198261</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>244383</t>
+          <t>242770</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>274558</t>
+          <t>274571</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>315817</t>
+          <t>314002</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>315919</t>
+          <t>316588</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>358500</t>
+          <t>357465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>604219</t>
+          <t>604640</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>660975</t>
+          <t>658406</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>147506</t>
+          <t>147882</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>184966</t>
+          <t>182488</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>124118</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>158929</t>
+          <t>159274</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>284380</t>
+          <t>282586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>331643</t>
+          <t>332522</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>29671</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>48819</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34375</t>
+          <t>34119</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>51071</t>
+          <t>51807</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>76195</t>
+          <t>77721</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>13490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22850</t>
+          <t>22981</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31479</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60094</t>
+          <t>60186</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76681</t>
+          <t>76548</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60486</t>
+          <t>59420</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79227</t>
+          <t>79862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123665</t>
+          <t>125254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149979</t>
+          <t>150179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,88%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18462</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27040</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44662</t>
+          <t>43198</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48723</t>
+          <t>48700</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71713</t>
+          <t>71175</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14148</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27348</t>
+          <t>27765</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33268</t>
+          <t>33940</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35811</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56085</t>
+          <t>57268</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70453</t>
+          <t>71139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90915</t>
+          <t>91191</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90749</t>
+          <t>91507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113902</t>
+          <t>113485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167372</t>
+          <t>167544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198216</t>
+          <t>198949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,61%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37136</t>
+          <t>37336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54577</t>
+          <t>55303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57847</t>
+          <t>59308</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80838</t>
+          <t>80772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108140</t>
+          <t>107403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19689</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34523</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>23569</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33186</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53172</t>
+          <t>52961</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>23739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24098</t>
+          <t>23125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40590</t>
+          <t>40133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55916</t>
+          <t>56665</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73273</t>
+          <t>73286</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64099</t>
+          <t>64329</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82560</t>
+          <t>81581</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>124648</t>
+          <t>124901</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>150011</t>
+          <t>151367</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,62%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>31057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>47157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>29225</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45906</t>
+          <t>46200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64143</t>
+          <t>65450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86595</t>
+          <t>88517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10959</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>21638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24811</t>
+          <t>24743</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>19372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34539</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55723</t>
+          <t>54356</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83668</t>
+          <t>85698</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107360</t>
+          <t>107908</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78100</t>
+          <t>78970</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99185</t>
+          <t>100174</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>170953</t>
+          <t>169534</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>202978</t>
+          <t>201738</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39666</t>
+          <t>39984</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59870</t>
+          <t>59327</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36239</t>
+          <t>36115</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55205</t>
+          <t>56027</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>80507</t>
+          <t>80162</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>109766</t>
+          <t>108584</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>18908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34428</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73021</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69355</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98856</t>
+          <t>99014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126880</t>
+          <t>128304</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>163794</t>
+          <t>164429</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>290351</t>
+          <t>290461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>331169</t>
+          <t>328551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>312317</t>
+          <t>312503</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>353543</t>
+          <t>353626</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>615312</t>
+          <t>615551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>670914</t>
+          <t>672474</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>139862</t>
+          <t>142594</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>175718</t>
+          <t>177703</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>147728</t>
+          <t>147562</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>184975</t>
+          <t>183915</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>298482</t>
+          <t>297469</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>349991</t>
+          <t>348133</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>64317</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52798</t>
+          <t>54212</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>80620</t>
+          <t>80365</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>111083</t>
+          <t>111073</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
